--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:20:05+00:00</t>
+    <t>2026-07-28T10:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -49,7 +49,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:50:36+00:00</t>
+    <t>2026-07-29T08:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries no display terms, which are supplied at expansion time by the implementer's own terminology server. Implementers must hold the applicable third-party licences.</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -351,14 +354,16 @@
       <c r="A13" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -377,7 +382,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>20</v>
@@ -385,10 +390,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -401,10 +406,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -423,7 +428,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>20</v>
@@ -431,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -445,10 +450,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:35:16+00:00</t>
+    <t>2026-07-29T12:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries no display terms, which are supplied at expansion time by the implementer's own terminology server. Implementers must hold the applicable third-party licences.</t>
+    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries, for some members, the SNOMED CT International Edition English term as an unmodified display hint (not translated); the authoritative display is supplied at expansion time by the implementer's own terminology server. Implementers must hold the applicable third-party licences.</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T12:05:46+00:00</t>
+    <t>2026-07-31T09:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0</t>
+    <t>1.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:21:13+00:00</t>
+    <t>2026-08-13T14:00:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:00:50+00:00</t>
+    <t>2026-08-13T23:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries, for some members, the SNOMED CT International Edition English term as an unmodified display hint (not translated); the authoritative display is supplied at expansion time by the implementer's own terminology server. Implementers must hold the applicable third-party licences.</t>
+    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries, for some members, the SNOMED CT International Edition English term as an unmodified display hint (not translated); the authoritative display is supplied at expansion time by the implementer's own terminology server. SNOMED CT® is a registered trademark of SNOMED International; those terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0, https://creativecommons.org/licenses/by-nd/4.0/) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers must hold the applicable third-party licences.</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.2</t>
+    <t>1.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:31:20+00:00</t>
+    <t>2026-08-14T00:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.3</t>
+    <t>1.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:08:39+00:00</t>
+    <t>2026-08-14T00:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.4</t>
+    <t>1.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:48:45+00:00</t>
+    <t>2026-08-15T14:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.5</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-15T14:40:00+00:00</t>
+    <t>2026-08-18T10:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.3.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T10:55:39+00:00</t>
+    <t>2026-08-18T13:05:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.1</t>
+    <t>1.3.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:05:08+00:00</t>
+    <t>2026-08-18T14:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-aspiration-risk-value-vs.xlsx
+++ b/ValueSet-aspiration-risk-value-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.2</t>
+    <t>1.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T14:23:53+00:00</t>
+    <t>2026-08-19T10:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
